--- a/12602928.xlsx
+++ b/12602928.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,15 @@
   </si>
   <si>
     <t>today is my last day of suspention</t>
+  </si>
+  <si>
+    <t>I feels good coming to class after long time</t>
+  </si>
+  <si>
+    <t>Happy</t>
+  </si>
+  <si>
+    <t>i gave presentation today</t>
   </si>
 </sst>
 </file>
@@ -2761,7 +2770,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="11">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="E30" s="11">
         <v>30</v>
@@ -2795,50 +2804,96 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" ht="28.8" spans="1:14">
       <c r="A31" s="15">
         <v>46286</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12" t="str">
+      <c r="B31" s="11">
+        <v>360</v>
+      </c>
+      <c r="C31" s="11">
+        <v>60</v>
+      </c>
+      <c r="D31" s="11">
+        <v>120</v>
+      </c>
+      <c r="E31" s="11">
+        <v>60</v>
+      </c>
+      <c r="F31" s="11">
+        <v>250</v>
+      </c>
+      <c r="G31" s="11">
+        <v>5</v>
+      </c>
+      <c r="H31" s="11">
+        <v>180</v>
+      </c>
+      <c r="I31" s="12">
+        <v>1030</v>
+      </c>
+      <c r="J31" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="14"/>
+        <v>410</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="15">
         <v>46287</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12" t="str">
+      <c r="B32" s="11">
+        <v>360</v>
+      </c>
+      <c r="C32" s="11">
+        <v>60</v>
+      </c>
+      <c r="D32" s="11">
+        <v>60</v>
+      </c>
+      <c r="E32" s="11">
+        <v>60</v>
+      </c>
+      <c r="F32" s="11">
+        <v>350</v>
+      </c>
+      <c r="G32" s="11">
+        <v>7</v>
+      </c>
+      <c r="H32" s="11">
+        <v>60</v>
+      </c>
+      <c r="I32" s="12">
         <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="12" t="str">
+        <v>950</v>
+      </c>
+      <c r="J32" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="14"/>
+        <v>490</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="15">
@@ -10982,13 +11037,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K8 K10:K15 K17:K22 K24:K29 K31:K36 K37:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K8 K10:K15 K17:K22 K24:K29 K31:K401">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L15 L16:L22 L23:L29 L30:L36 L37:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M15 M16:M22 M23:M29 M30:M36 M37:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
